--- a/daily_matches/job_matches_2026-09-11.xlsx
+++ b/daily_matches/job_matches_2026-09-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Korean Bilingual Jr. AI Developer</t>
+          <t>Junior Full Stack Software Engineer AI and Cloud Applications</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>Agility Technologies Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1da70a3cd36c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2063590dad13da</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow, CI/CD</t>
+          <t>Data Scientist, RAG, Redshift, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Redshift, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e40d6c2946e491bb</t>
+          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jr. AI Developer (W2)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopaq Logic</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, RAG, Redshift, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Redshift, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcc54287680ef3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3c059719ff1f4a84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Application Engineer II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Canon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, BigQuery, Git, BigQuery, Hadoop, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5faae4e8dc380d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, S3, EC2, Docker, CI/CD, Databricks, NoSQL</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b616b3895ec311e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Accelerator Intern</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The RealReal</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, AKS, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, EC2, Redshift, Data Lake, Git, Redshift, Hadoop, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5944258f157b901</t>
+          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Azure dotNet AI Integration Developer</t>
+          <t>Forward Deployed Software Engineer - Equities Technology</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Berlin Packaging</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, Databricks, Kafka, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc29c100a8b89c42</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ef51fce4a7feef</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Software Engineer Azure &amp; Microsoft Cloud</t>
+          <t>Cloud Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Leggett &amp; Platt</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, SQL, R</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bdf03283a9a5d27</t>
+          <t>https://www.indeed.com/viewjob?jk=e4f31e377e81e5d6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Microservices</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL</t>
+          <t>Machine Learning Engineer, RAG, Docker, CI/CD, Jenkins, Git, Snowflake, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8e3e233479d613</t>
+          <t>https://www.indeed.com/viewjob?jk=c35b053cf5169d36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Graph AI Platforms | Onsite - (Dallas, Charlotte, New York)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Hadoop, Python, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, PyTorch, Kubernetes, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
+          <t>https://www.indeed.com/viewjob?jk=90572b8a295444fd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ph.D. Intern - AI/ML &amp; Design Automation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
+          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb85da3f06321f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d3138439a8084fb3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java Microservices</t>
+          <t>Senior Software Engineer, AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, FastAPI, CI/CD, Snowflake, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a42ca990ed148f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f29bf405f23dd7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Senior Software Developer Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Inter-American Development Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
+          <t>https://www.indeed.com/viewjob?jk=3497e66f46643ee4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Python/Django ReactJS Website Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e15f5d9b977a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=671809c3ed9455ee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - AI &amp; Search</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Apache Airflow, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198a1d32c3c5a248</t>
+          <t>https://www.indeed.com/viewjob?jk=b5b8da1e0e6a3f8e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1aa506486aae49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Architect – Data Analytics (Remote)</t>
+          <t>IDB. AI for Financial Intelligence, Knowledge Graphs and Data Integration Intern</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Inter-American Development Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Power BI, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, PyTorch, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
+          <t>https://www.indeed.com/viewjob?jk=ef35f06e9610b43f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LexisNexis Reed Tech</t>
+          <t>LEMNIS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,94 +1091,94 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
+          <t>https://www.indeed.com/viewjob?jk=363db9be69e605b3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Core Infrastructure, AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Apache Airflow, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff7ed7ce6374b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=06bf0c7da91d84a9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Agentic AI Developers</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Persistent Systems</t>
+          <t>Brillient Corporation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hyattsville, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, CI/CD, Git, BigQuery, Python, R, Java</t>
+          <t>Data Scientist, RAG, Kubernetes, Apache Airflow, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9ba41ed9da2d76</t>
+          <t>https://www.indeed.com/viewjob?jk=89d682e04f548bac</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist I - Customer Lifecycle</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cda1b8801460b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=29b6067d33a02968</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>AI/ML Engineering Intern - (Baton Rouge, LA/Frederick, MD)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473f1fb048156c22</t>
+          <t>https://www.indeed.com/viewjob?jk=726973a9b8c78e5e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>AI/ML Engineering Intern - (Baton Rouge, LA/Frederick, MD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fe98426fa26ae17</t>
+          <t>https://www.indeed.com/viewjob?jk=2d9936269acdbc26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Test Automation Engineer / Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stored Energy Systems</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, R, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860a5ffad8b39c04</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d20bafae27811d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Test Automation Engineer / Architect</t>
+          <t>Senior Software Engineer - Blockchain</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433dba1f723a1ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=19ee4827fe3544f2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Redshift, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cdfd62ebd565b7</t>
+          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>REPAY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c7873bbb81e0d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer, Information Technology</t>
+          <t>Associate, Software Engineer SCDT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Heritage Foundation</t>
+          <t>Alcon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Glue, Data Lake, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb707f57e3c694f</t>
+          <t>https://www.indeed.com/viewjob?jk=c858960802f25711</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Specialist - Data Sciences</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Crane Aerospace &amp; Electronics</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lynnwood, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Java, Hypothesis Testing</t>
+          <t>Synapse, Data Lake, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5172fdfd63d9f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist I - Epic Model Monitoring</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Skokie, IL, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Data Lake, Git, Snowflake, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,77 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8fbee8bc45bc14</t>
+          <t>https://www.indeed.com/viewjob?jk=4117bea865498bcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PhD Intern - Data Scientist &amp; Generative AI in Femcare</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, PyTorch, Git, Python, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e27f962aed198f5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Technology Business Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ochsner Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Jefferson, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Snowflake, Databricks, Tableau, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-11.xlsx
+++ b/daily_matches/job_matches_2026-09-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior Full Stack Software Engineer AI and Cloud Applications</t>
+          <t>GenAI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Agility Technologies Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2063590dad13da</t>
+          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI /ML Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Redshift, Hadoop</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GenAI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Redshift, Hadoop</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c059719ff1f4a84</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbc2ded1357ab6b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI /ML Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Canon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, BigQuery, Git, BigQuery, Hadoop, Tableau</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,94 +601,94 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5faae4e8dc380d</t>
+          <t>https://www.indeed.com/viewjob?jk=386200b3002aff99</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Tableau, Power BI</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>EIS Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Redshift, Data Lake, Git, Redshift, Hadoop, NoSQL</t>
+          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6ad6527a71b393</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer - Equities Technology</t>
+          <t>Senior Software Engineer II (Data Pipelines)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ef51fce4a7feef</t>
+          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer III</t>
+          <t>GenAI Test Automation Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4f31e377e81e5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=57c8ee6add47b13e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, CI/CD, Jenkins, Git, Snowflake, MySQL, MongoDB, NoSQL</t>
+          <t>Data Scientist, Generative AI, LangChain, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c35b053cf5169d36</t>
+          <t>https://www.indeed.com/viewjob?jk=11f9d5723a1f947a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Graph AI Platforms | Onsite - (Dallas, Charlotte, New York)</t>
+          <t>Forward Developed Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, PyTorch, Kubernetes, CI/CD, Git, Python, SQL</t>
+          <t>AI Engineer, RAG, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90572b8a295444fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9d1ab5ee809ca2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI/Automation Intern - Summer 2027</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Cox Enterprises</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, Prompt Engineering, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3138439a8084fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=07f1d96c479c1a95</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI</t>
+          <t>Senior Associate Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, FastAPI, CI/CD, Snowflake, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Databricks, Hadoop, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f29bf405f23dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=1944941e434f6d92</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Developer Consultant</t>
+          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Inter-American Development Bank</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3497e66f46643ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=181c999619cfab66</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671809c3ed9455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ceae118c7c7bf2eb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI &amp; Search</t>
+          <t>Senior Data Scientist - Agentic AI &amp; Decision Intelligence</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5b8da1e0e6a3f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=72827f91736b9d42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>UDCYDE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1aa506486aae49</t>
+          <t>https://www.indeed.com/viewjob?jk=3eea344395d8c614</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IDB. AI for Financial Intelligence, Knowledge Graphs and Data Integration Intern</t>
+          <t>Senior Software Engineer, Agentic AI and Observability</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Inter-American Development Bank</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, PyTorch, Git, Power BI, Python, SQL</t>
+          <t>LangChain, LLaMA, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef35f06e9610b43f</t>
+          <t>https://www.indeed.com/viewjob?jk=3afba161bc78c1fb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Activision 2027 Summer Internships - Analytics Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LEMNIS</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Python, SQL, R</t>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363db9be69e605b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a151a475ceda8359</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer, Core Infrastructure, AI</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Kafka, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bf0c7da91d84a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b7deca92f2c7f41e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Brillient Corporation</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hyattsville, MD, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, Apache Airflow, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, PySpark, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,427 +1161,42 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d682e04f548bac</t>
+          <t>https://www.indeed.com/viewjob?jk=5141a554cf1e2b91</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist I - Customer Lifecycle</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Persistent Systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, S3, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2022-07-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b6067d33a02968</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AI/ML Engineering Intern - (Baton Rouge, LA/Frederick, MD)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Frederick, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=726973a9b8c78e5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI/ML Engineering Intern - (Baton Rouge, LA/Frederick, MD)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Baton Rouge, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d9936269acdbc26</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Stored Energy Systems</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Longmont, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d20bafae27811d</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Blockchain</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19ee4827fe3544f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>RS21: A Data Science and Visualization Company</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Redshift, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>REPAY</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Associate, Software Engineer SCDT</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Alcon</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Glue, Data Lake, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c858960802f25711</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Crane Aerospace &amp; Electronics</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Lynnwood, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Synapse, Data Lake, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>AstraZeneca</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Frederick, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4117bea865498bcf</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>PhD Intern - Data Scientist &amp; Generative AI in Femcare</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Procter &amp; Gamble</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, PyTorch, Git, Python, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e27f962aed198f5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Technology Business Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Ochsner Health</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Jefferson, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Snowflake, Databricks, Tableau, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d3c4a3018e6e4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-11.xlsx
+++ b/daily_matches/job_matches_2026-09-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Data Scientist</t>
+          <t>Senior Software Engineer - AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering, spaCy, NLTK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI /ML Data Scientist</t>
+          <t>Consultant, Data Engineer | Snowflake Data Engineer (Python / Snowpark)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
+          <t>AI Engineer, Data Scientist, RAG, S3, EC2, Redshift, Apache Airflow, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,137 +531,137 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3affdaaa77646055</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Data Scientist</t>
+          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
+          <t>LangChain, RAG, Gemini, Prompt Engineering, BigQuery, CI/CD, Git, BigQuery, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbc2ded1357ab6b</t>
+          <t>https://www.indeed.com/viewjob?jk=7243ca669e449c88</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI /ML Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386200b3002aff99</t>
+          <t>https://www.indeed.com/viewjob?jk=6eab47ece7c9f23b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8fccc8f57dde6104</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EIS Group</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL</t>
+          <t>RAG, S3, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6ad6527a71b393</t>
+          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II (Data Pipelines)</t>
+          <t>Data Scientist, Business &amp; Product</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, PostgreSQL, Python</t>
+          <t>Data Scientist, BigQuery, CI/CD, Snowflake, BigQuery, Tableau, Python, SQL, R, Bayesian</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,497 +706,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
+          <t>https://www.indeed.com/viewjob?jk=4f6122d1d15bcca7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GenAI Test Automation Architect</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R</t>
+          <t>RAG, Glue, MLflow, Kubernetes, AKS, Snowflake, Databricks, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c8ee6add47b13e</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Zoom Communications</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11f9d5723a1f947a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Forward Developed Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9d1ab5ee809ca2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AI/Automation Intern - Summer 2027</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Cox Enterprises</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, Prompt Engineering, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07f1d96c479c1a95</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Databricks, Hadoop, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1944941e434f6d92</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=181c999619cfab66</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ceae118c7c7bf2eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Agentic AI &amp; Decision Intelligence</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Wellesley, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Snowflake, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72827f91736b9d42</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>UDCYDE</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, MySQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3eea344395d8c614</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Agentic AI and Observability</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LangChain, LLaMA, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3afba161bc78c1fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Activision 2027 Summer Internships - Analytics Engineering</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Activision</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Santa Monica, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a151a475ceda8359</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ZoomInfo</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Kafka, MongoDB, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7deca92f2c7f41e</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Engineer - Finance AI Solutions</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Brooklyn Park, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, PySpark, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5141a554cf1e2b91</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Java Developer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Persistent Systems</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, Kubernetes, CI/CD, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2022-07-04</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d3c4a3018e6e4</t>
+          <t>https://www.indeed.com/viewjob?jk=5b92f63d41ceba18</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-11.xlsx
+++ b/daily_matches/job_matches_2026-09-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering, spaCy, NLTK</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b781c227580f9b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Snowflake Data Engineer (Python / Snowpark)</t>
+          <t>Sr. Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Connexity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, S3, EC2, Redshift, Apache Airflow, CI/CD, Jenkins, Git</t>
+          <t>RAG, Copilot, BigQuery, Git, BigQuery, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3affdaaa77646055</t>
+          <t>https://www.indeed.com/viewjob?jk=aa04adb1964f53c0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Prompt Engineering, BigQuery, CI/CD, Git, BigQuery, NoSQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, AWS SageMaker, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7243ca669e449c88</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c6ce0d14df9eef</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer (Early Career)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Nerdio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>AI Engineer, RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eab47ece7c9f23b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f7e21d15f7b0486</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Application Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Tax Analysts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>S3, Docker, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fccc8f57dde6104</t>
+          <t>https://www.indeed.com/viewjob?jk=a15500b620e2abbe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,77 +671,252 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
+          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist, Business &amp; Product</t>
+          <t>AI Automation Engineering with Cyber Security</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, BigQuery, CI/CD, Snowflake, BigQuery, Tableau, Python, SQL, R, Bayesian</t>
+          <t>Generative AI, RAG, Copilot, S3, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f6122d1d15bcca7</t>
+          <t>https://www.indeed.com/viewjob?jk=53f414c598f70958</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Scientist Intern, Applied AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Envita Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Prompt Engineering, TensorFlow, PyTorch, Docker, Git, Seaborn, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18fb2dfb919586f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Agent Engineer, Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Orbis Operations</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbb5128a246a450a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>POOLCORP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Covington, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mirantis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca39720d41d00c5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Associate, Artificial Intelligence Engineering</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Options Clearing Corporation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Glue, MLflow, Kubernetes, AKS, Snowflake, Databricks, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b92f63d41ceba18</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65bdcc9f45a04bca</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer (iOS &amp; Scala)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, MySQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2db5376d37406ad6</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-11.xlsx
+++ b/daily_matches/job_matches_2026-09-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow, Databricks</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b781c227580f9b</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2ac2b347d252fa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Backend</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Connexity</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Git, BigQuery, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, spaCy, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa04adb1964f53c0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc92810152cc5a91</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer, Data - SF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, AWS SageMaker, CI/CD, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Prompt Engineering, BigQuery, Dataflow, Docker, Kubernetes, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c6ce0d14df9eef</t>
+          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solutions Engineer (Early Career)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nerdio</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f7e21d15f7b0486</t>
+          <t>https://www.indeed.com/viewjob?jk=99abac312f847817</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, Application Platform</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tax Analysts</t>
+          <t>PathAI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Docker, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15500b620e2abbe</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfa29b4a880dee4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>AI Software Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>PURIS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>The Woodlands, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, LLaMA, Redshift, Synapse, Snowflake, Databricks, Redshift, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
+          <t>https://www.indeed.com/viewjob?jk=8a14a0366d22262f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Automation Engineering with Cyber Security</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, S3, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Synapse, CI/CD, Git, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f414c598f70958</t>
+          <t>https://www.indeed.com/viewjob?jk=d533eaa4f42204d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist Intern, Applied AI</t>
+          <t>Senior Dynamics 365 - Power Platform Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Envita Solutions</t>
+          <t>AHU Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Prompt Engineering, TensorFlow, PyTorch, Docker, Git, Seaborn, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Synapse, CI/CD, GitHub Actions, Terraform, Git, Power BI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18fb2dfb919586f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Agent Engineer, Cloud Infrastructure</t>
+          <t>CFSA Senior Developer D365 Power Platform Azure</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Orbis Operations</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Synapse, CI/CD, GitHub Actions, Terraform, Git, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb5128a246a450a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>POOLCORP</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Covington, LA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Jenkins, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3789928e4cd20157</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Korean Bilingual Sr. AI DevOps Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca39720d41d00c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1baadba314a09d05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Associate, Artificial Intelligence Engineering</t>
+          <t>Software Engineer - Platform Foundation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Blend Labs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,917 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65bdcc9f45a04bca</t>
+          <t>https://www.indeed.com/viewjob?jk=668e8653cee4c021</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (iOS &amp; Scala)</t>
+          <t>Machine Learning Engineer II - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b76891041fec73a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Data Management</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CoStar Group</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Azure ML, S3, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Databricks Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=213eeef2d3afc755</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Databricks Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a32584106a1cad30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Solutions Architect, Executive Briefing Center</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LangChain, LLaMA, PyTorch, Kubernetes, CI/CD, Git, Dask, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff703db67b38300f</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QAE/DevOps Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>G.E.H.A</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1353f557748d76af</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, HR Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FTI Consulting, Inc.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Data Lake, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12df59b44e06ccc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Engineer AI Native Delivery</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Taazaa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Hudson, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FDM Group</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8fa6c5fb4de045e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer - Agent Platform</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=776c829bf011fe27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brooks Automation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09ff6cda02fdee2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist Real Estate</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Academy Sports + Outdoors</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Katy, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Prompt Engineering, BigQuery, Git, BigQuery, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81728ae55fa08d8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Git, Snowflake, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6777f8c12f19163a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Architect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Clarity Innovations, LLC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Springfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, MySQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2db5376d37406ad6</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=615e1448773a39c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Scientist - Databricks Genie &amp; AI Analytics</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Dev Technology Group</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Databricks, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb2f0ad851bda298</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Engineer | Enterprise Technology &amp; Security Development Program</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Snowflake, Kafka, Hadoop, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d34f2f462d2286e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer / Architect</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Infopro Digital</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MTS, Machine Learning</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, S3, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfecaa951490da42</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Financial Analyst – Advanced Analytics &amp; BI</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, BigQuery, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c6289320e9f1691</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Marketing Data Scientist</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f05e06ccb0f7e4c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Test Automation Engineer - Playwright</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2657b48b28744870</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Metrc</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Lakeland, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df67af954ac80b99</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, GitHub Actions, Git, Kafka, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94f038028488e551</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Cloud Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da8e863d0df9290d</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Cloud Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7af1e139bcd61770</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AI Engineer, Architect</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Clarity Innovations, LLC</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Springfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fe8980c969292d6</t>
         </is>
       </c>
     </row>
